--- a/reports/一级子公司A_现金流量表_2026-03.xlsx
+++ b/reports/一级子公司A_现金流量表_2026-03.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>152646000</v>
+        <v>150008090</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>421302960</v>
+        <v>415701885</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3008611</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>8271863</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1490181</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>4126427</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>752478</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2071996</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>596431</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1648082</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>450783</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1244319</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>298925</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>823869</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>224734</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>621844</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>149939</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>412420</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>373396</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1034632</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>188892</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>519249</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>118482</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>328228</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>391400</v>
+        <v>387930</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1080264</v>
+        <v>1067487</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2781000</v>
+        <v>2731866</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>7675560</v>
+        <v>7554959</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>155818400</v>
+        <v>160780738</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>98880000</v>
+        <v>97333938</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>272908800</v>
+        <v>269617120</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1001509</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>2753123</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>745655</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2066214</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>501619</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1379622</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>372534</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1030982</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>250750</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>690969</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>187456</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>517548</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16171000</v>
+        <v>15994677</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>44631960</v>
+        <v>44188267</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8240000</v>
+        <v>8118096</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>22742400</v>
+        <v>22357128</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3399000</v>
+        <v>3351842</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>9381240</v>
+        <v>9280246</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>126690000</v>
+        <v>127858076</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>29128400</v>
+        <v>32922662</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185400</v>
+        <v>183616</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>556200</v>
+        <v>550907</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1545000</v>
+        <v>1524682</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>4635000</v>
+        <v>4586118</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>947600</v>
+        <v>936089</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>2842800</v>
+        <v>2798295</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1730400</v>
+        <v>1708298</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14420000</v>
+        <v>14234859</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>43260000</v>
+        <v>42525306</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2060000</v>
+        <v>2014533</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>6180000</v>
+        <v>6067211</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10300000</v>
+        <v>10185642</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>30900000</v>
+        <v>30460957</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>391400</v>
+        <v>386585</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1174200</v>
+        <v>1161911</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14811400</v>
+        <v>14621444</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-13081000</v>
+        <v>-12913146</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3605000</v>
+        <v>3545110</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>10815000</v>
+        <v>10679710</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5665000</v>
+        <v>5562118</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>16995000</v>
+        <v>16733989</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5665000</v>
+        <v>5615803</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>16995000</v>
+        <v>16819017</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>185400</v>
+        <v>182312</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>556200</v>
+        <v>547138</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9455400</v>
+        <v>9289540</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4635000</v>
+        <v>4570411</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>13905000</v>
+        <v>13680304</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4635000</v>
+        <v>4572198</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>13905000</v>
+        <v>13761569</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>741600</v>
+        <v>733584</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2224800</v>
+        <v>2192061</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>648900</v>
+        <v>643350</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>1946700</v>
+        <v>1922268</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>92700</v>
+        <v>91047</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>278100</v>
+        <v>274090</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5469300</v>
+        <v>5395042</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3986100</v>
+        <v>3894498</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>20033500</v>
+        <v>23904014</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>20033500</v>
+        <v>23904014</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
